--- a/data/xlsx/KNF_Rejestr_posrednikow_ubezpieczeniowych_agent.xlsx
+++ b/data/xlsx/KNF_Rejestr_posrednikow_ubezpieczeniowych_agent.xlsx
@@ -217,7 +217,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1234884655</t>
+          <t>2234884655</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2235676551</t>
+          <t>1235676551</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>07-09-2016</t>
+          <t/>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0000003112</t>
+          <t>000000311</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>000000456</t>
+          <t>0000004567</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1238764965</t>
+          <t>2238764965</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2239556861</t>
+          <t>1239556861</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0000007962</t>
+          <t>000000796</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>000000941</t>
+          <t>0000009417</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>75032139753</t>
+          <t>65032139753</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>1242645273</t>
+          <t>2242645273</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2243516365</t>
+          <t>1243516365</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -9629,7 +9629,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>0000012812</t>
+          <t>000001281</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -10672,7 +10672,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>78042806868</t>
+          <t>68042806868</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -10709,7 +10709,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>000001426</t>
+          <t>0000014267</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>1246525583</t>
+          <t>2246525583</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2247396679</t>
+          <t>1247396679</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -13229,7 +13229,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0000017662</t>
+          <t>000001766</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>81050774016</t>
+          <t>71050774016</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -14309,7 +14309,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>000001911</t>
+          <t>0000019117</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -14329,7 +14329,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>1250405891</t>
+          <t>2250405891</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">

--- a/data/xlsx/KNF_Rejestr_posrednikow_ubezpieczeniowych_agent.xlsx
+++ b/data/xlsx/KNF_Rejestr_posrednikow_ubezpieczeniowych_agent.xlsx
@@ -4509,7 +4509,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>UINQ T ..</t>
+          <t>UI  ..</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>sooba fziyczna</t>
+          <t>sooba fziyczan</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">

--- a/data/xlsx/KNF_Rejestr_posrednikow_ubezpieczeniowych_agent.xlsx
+++ b/data/xlsx/KNF_Rejestr_posrednikow_ubezpieczeniowych_agent.xlsx
@@ -165,12 +165,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Kowalska-Krawczyk</t>
+          <t>Lewandowska-Król</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>60021406849</t>
+          <t>62021428841</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -192,7 +192,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zielony Bieszczady S.A.</t>
+          <t>Pewny Delfin S.A.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -242,12 +242,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Nowacki</t>
+          <t>Zieliński</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>61032108236</t>
+          <t>63032130231</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -269,7 +269,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Zielony Karpaty SA</t>
+          <t>Dobry Koral SA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -319,12 +319,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Wiśniewska</t>
+          <t>Szymańska</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>62042809586</t>
+          <t>64042831581</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -346,7 +346,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zielony Bałtyk S. A.</t>
+          <t>Polski Szafir S. A.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -396,12 +396,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Dąbrowski</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>63050710972</t>
+          <t>65050732974</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -423,7 +423,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zielony Sudety Spółka Akcyjna</t>
+          <t>Europejski Orzeł Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -473,12 +473,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Mazur</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>64061412321</t>
+          <t>66061434323</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Niebieski Amber sp. z o.o.</t>
+          <t>Globalny Kaktus sp. z o.o.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -550,12 +550,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Kamiński</t>
+          <t>Krawczyk</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>65072113717</t>
+          <t>67072135719</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Niebieski Bizon sp z oo</t>
+          <t>Lokalny Olimp sp z oo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -627,12 +627,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Lewandowska</t>
+          <t>Woźniak</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>66082815068</t>
+          <t>68082837060</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Niebieski Canyon sp. z . o.</t>
+          <t>Nowoczesny Beskid sp. z o. o.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>perzsiędbiorca</t>
+          <t>persziędbiorca</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Maerk</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Zieliński</t>
+          <t>Jankowski</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>67090716451</t>
+          <t>69090738453</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Niebieski Delfin Sp. z o.o.</t>
+          <t>Tradycyjny Canyon Sp. z o.o.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Szymańska</t>
+          <t>Grabowska</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>68101417802</t>
+          <t>70101439803</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Niebieski Echo SP Z O O</t>
+          <t>Dynamiczny Jantar SP Z O O</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Dąbrowski</t>
+          <t>Pawlak</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>69112119190</t>
+          <t>71112141194</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Niebieski Falcon spółka z ograniczoną odpowiedzialnością</t>
+          <t>Stabilny Rubin spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -935,12 +935,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Michalska</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>70122820541</t>
+          <t>72122842543</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Niebieski Gryf Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Innowacyjny Sokół Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Król</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>71010721939</t>
+          <t>73010743931</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Niebieski Horyzont S.A.</t>
+          <t>Kreatywny Jodełka S.A.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Wieczorek</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>72021423289</t>
+          <t>74021445281</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Niebieski Ikar SA</t>
+          <t>Aktywny Zodiak SA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1166,12 +1166,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Jankowski</t>
+          <t>Jabłoński</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>73032124675</t>
+          <t>75032146677</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Niebieski Jantar S. A.</t>
+          <t>Jasny Kasprowy S. A.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Grabowska</t>
+          <t>Witkowska</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>74042826025</t>
+          <t>76042848027</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Niebieski Koral Spółka Akcyjna</t>
+          <t>Green Bizon Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1320,12 +1320,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Pawlak</t>
+          <t>Walczak</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>75050727418</t>
+          <t>77050749410</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Niebieski Lotos sp. z o.o.</t>
+          <t>Blue Ikar sp. z o.o.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1397,12 +1397,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Michalska</t>
+          <t>Stępień</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>76061428767</t>
+          <t>78061450762</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Niebieski Magnolia sp z oo</t>
+          <t>Gold Pegaz sp z oo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>WARTA S.A.</t>
+          <t/>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1474,12 +1474,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Baran</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>77072130157</t>
+          <t>79072152159</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Niebieski Neon sp. z o. o.</t>
+          <t>Silver Żubr sp. z o. o.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Rutkowska</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>78082831506</t>
+          <t>80082853507</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Niebieski Oaza Sp. z o.o.</t>
+          <t>Smart Narew Sp. z o.o.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1628,12 +1628,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Jabłoński</t>
+          <t>Górski</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>79090732890</t>
+          <t>81090754891</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>P.P.H.U. Niebieski Pegaz</t>
+          <t>P.P.H.U. Fast Syrena</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1705,12 +1705,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Witkowska</t>
+          <t>Sikora</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>80101434241</t>
+          <t>82101456243</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Niebieski Rubin spółka z ograniczoną odpowiedzialnością</t>
+          <t>Safe Rysy spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Ostrowski</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>81112135637</t>
+          <t>83112157639</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Niebieski Szafir Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Best Amber Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1859,12 +1859,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Tomaszewska</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>82122836987</t>
+          <t>84122858989</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Niebieski Tytan S.A.</t>
+          <t>Global Horyzont S.A.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Zając</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>83010738376</t>
+          <t>85010760371</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Niebieski Uran SA</t>
+          <t>Future Oaza SA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2013,12 +2013,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Rutkowska</t>
+          <t>Pietrzak</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>84021439724</t>
+          <t>86021461729</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Niebieski Wektor S. A.</t>
+          <t>Wielkopolski Zefir S. A.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2090,12 +2090,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Górski</t>
+          <t>Wójcicki</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>85032141114</t>
+          <t>87032163116</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Niebieski Zefir Spółka Akcyjna</t>
+          <t>Śląski Pilica Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Czarnecka</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>86042842464</t>
+          <t>88042864466</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Niebieski Żubr sp. z o.o.</t>
+          <t>Mazowiecki Marmur sp. z o.o.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Ostrowski</t>
+          <t>Lis</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>87050743857</t>
+          <t>89050765859</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Niebieski Sokół sp z oo</t>
+          <t>Pomorski Giewont sp z oo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Tomaszewska</t>
+          <t>Kołodziej</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>88061445206</t>
+          <t>90061467207</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Niebieski Orzeł sp. z o. o.</t>
+          <t>Dolnośląski Sudety sp. z o. o.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2398,12 +2398,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Kaczmarek</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>89072146593</t>
+          <t>91072168594</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Niebieski Kormoran Sp. z o.o.</t>
+          <t>Karpacki Gryf Sp. z o.o.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Niebieski Barycz SP Z O O</t>
+          <t>Bałtycki Neon SP Z O O</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Niebieski Noteć spółka z ograniczoną odpowiedzialnością</t>
+          <t>Młody Wektor spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Niebieski Pilica Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Wspólny Noteć Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Niebieski Narew S.A.</t>
+          <t>Pierwszy Granit S.A.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Niebieski Jodełka SA</t>
+          <t>Zielony Żubr SA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Niebieski Kaktus S. A.</t>
+          <t>Niebieski Narew S. A.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Niebieski Szmaragd Spółka Akcyjna</t>
+          <t>Złoty Syrena Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Niebieski Topaz sp. z o.o.</t>
+          <t>Srebrny Rysy sp. z o.o.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Niebieski Granit sp z oo</t>
+          <t>Czysty Amber sp z oo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Niebieski Syrena Sp. z o.o.</t>
+          <t>Pewny Oaza Sp. z o.o.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Niebieski Zodiak SP Z O O</t>
+          <t>Dobry Zefir SP Z O O</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Niebieski Olimp spółka z ograniczoną odpowiedzialnością</t>
+          <t>Polski Pilica spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Niebieski Zorza Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Europejski Marmur Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Niebieski Krokus S.A.</t>
+          <t>Globalny Giewont S.A.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Niebieski Narcyz SA</t>
+          <t>Lokalny Sudety SA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Niebieski Giewont S. A.</t>
+          <t>Nowoczesny Gryf S. A.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Niebieski Rysy Spółka Akcyjna</t>
+          <t>Tradycyjny Neon Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Niebieski Kasprowy sp. z o.o.</t>
+          <t>Dynamiczny Wektor sp. z o.o.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Amber Transport sp. z o. o.</t>
+          <t>Falcon Transport sp. z o. o.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Amber Spedycja Sp. z o.o.</t>
+          <t>Koral Spedycja Sp. z o.o.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Amber Logistyka SP Z O O</t>
+          <t>Pegaz Logistyka SP Z O O</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Amber Handel spółka z ograniczoną odpowiedzialnością</t>
+          <t>Wektor Handel spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Amber Usługi Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Kormoran Usługi Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Amber Finanse S.A.</t>
+          <t>Jodełka Finanse S.A.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Amber Doradztwo SA</t>
+          <t>Marmur Doradztwo SA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>przedsęiiborca</t>
+          <t>przesdęiiborca</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Amber Szkolenia S. A.</t>
+          <t>Krokus Szkolenia S. A.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Amber Media Spółka Akcyjna</t>
+          <t>Beskid Media Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Amber Marketing sp z oo</t>
+          <t>Falcon Marketing sp z oo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Amber Druk sp. z o. o.</t>
+          <t>Koral Druk sp. z o. o.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Amber Informatyka Sp. z o.o.</t>
+          <t>Pegaz Informatyka Sp. z o.o.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Amber Oprogramowanie SP Z O O</t>
+          <t>Wektor Oprogramowanie SP Z O O</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Amber Rolnictwo spółka z ograniczoną odpowiedzialnością</t>
+          <t>Kormoran Rolnictwo spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Amber Ogrodnictwo Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Jodełka Ogrodnictwo Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Amber Produkcja S.A.</t>
+          <t>Marmur Produkcja S.A.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Amber Przemysł SA</t>
+          <t>Krokus Przemysł SA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Amber Ekologia S. A.</t>
+          <t>Beskid Ekologia S. A.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Amber Instalacje sp. z o.o.</t>
+          <t>Falcon Instalacje sp. z o.o.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Amber Nieruchomości sp z oo</t>
+          <t>Koral Nieruchomości sp z oo</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Amber Inwestycje sp. z o. o.</t>
+          <t>Pegaz Inwestycje sp. z o. o.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Amber Medycyna Sp. z o.o.</t>
+          <t>Wektor Medycyna Sp. z o.o.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Amber Zdrowie SP Z O O</t>
+          <t>Kormoran Zdrowie SP Z O O</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Amber Urody spółka z ograniczoną odpowiedzialnością</t>
+          <t>Jodełka Urody spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Amber Turystyka Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Marmur Turystyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Amber Rozrywka S.A.</t>
+          <t>Krokus Rozrywka S.A.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Amber Gastronomia SA</t>
+          <t>Beskid Gastronomia SA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Amber Tekstylia Spółka Akcyjna</t>
+          <t>Falcon Tekstylia Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Amber Motoryzacja sp. z o.o.</t>
+          <t>Koral Motoryzacja sp. z o.o.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>16-400</t>
+          <t/>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t/>
+          <t>Przybylska</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Amber Ubezpieczenia sp z oo</t>
+          <t>Pegaz Ubezpieczenia sp z oo</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Amber Spawalnictwo sp. z o. o.</t>
+          <t>Wektor Spawalnictwo sp. z o. o.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Amber Ślusarstwo Sp. z o.o.</t>
+          <t>Kormoran Ślusarstwo Sp. z o.o.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Amber Krawiectwo SP Z O O</t>
+          <t>Jodełka Krawiectwo SP Z O O</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Amber Ochrona spółka z ograniczoną odpowiedzialnością</t>
+          <t>Marmur Ochrona spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Amber Catering Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Krokus Catering Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Amber Księgowość S.A.</t>
+          <t>Beskid Księgowość S.A.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Bizon Budownictwo SA</t>
+          <t>Jantar Budownictwo SA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Bizon Transport S. A.</t>
+          <t>Oaza Transport S. A.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bizon Spedycja Spółka Akcyjna</t>
+          <t>Uran Spedycja Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bizon Logistyka sp. z o.o.</t>
+          <t>Orzeł Logistyka sp. z o.o.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Bizon Handel sp z oo</t>
+          <t>Narew Handel sp z oo</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Bizon Usługi sp. z o. o.</t>
+          <t>Granit Usługi sp. z o. o.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Bizon Finanse Sp. z o.o.</t>
+          <t>Zorza Finanse Sp. z o.o.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Bizon Doradztwo SP Z O O</t>
+          <t>Kasprowy Doradztwo SP Z O O</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Bizon Szkolenia spółka z ograniczoną odpowiedzialnością</t>
+          <t>Sudety Szkolenia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Bizon Media Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Echo Media Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>P.P.H.U. Bizon Reklama</t>
+          <t>P.P.H.U. Jantar Reklama</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7892,7 +7892,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Bizon Marketing SA</t>
+          <t>Oaza Marketing SA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Bizon Druk S. A.</t>
+          <t>Uran Druk S. A.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Bizon Informatyka Spółka Akcyjna</t>
+          <t>Orzeł Informatyka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Bizon Oprogramowanie sp. z o.o.</t>
+          <t>Narew Oprogramowanie sp. z o.o.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Bizon Rolnictwo sp z oo</t>
+          <t>Granit Rolnictwo sp z oo</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Bizon Ogrodnictwo sp. z o. o.</t>
+          <t>Zorza Ogrodnictwo sp. z o. o.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Bizon Produkcja Sp. z o.o.</t>
+          <t>Kasprowy Produkcja Sp. z o.o.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>ERGO EHSTIA S.A.</t>
+          <t>ERGO HESTIA S.A.</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>os. Retkinia 140</t>
+          <t>os. Retkiina 140</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Bizon Przemysł SP Z O O</t>
+          <t>Sudety Przemysł SP Z O O</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Bizon Ekologia spółka z ograniczoną odpowiedzialnością</t>
+          <t>Echo Ekologia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Bizon Energetyka Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Jantar Energetyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Bizon Instalacje S.A.</t>
+          <t>Oaza Instalacje S.A.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Bizon Nieruchomości SA</t>
+          <t>Uran Nieruchomości SA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Bizon Inwestycje S. A.</t>
+          <t>Orzeł Inwestycje S. A.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -8893,7 +8893,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Bizon Medycyna Spółka Akcyjna</t>
+          <t>Narew Medycyna Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Bizon Zdrowie sp. z o.o.</t>
+          <t>Granit Zdrowie sp. z o.o.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -9047,7 +9047,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Bizon Urody sp z oo</t>
+          <t>Zorza Urody sp z oo</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Bizon Turystyka sp. z o. o.</t>
+          <t>Kasprowy Turystyka sp. z o. o.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Bizon Rozrywka Sp. z o.o.</t>
+          <t>Sudety Rozrywka Sp. z o.o.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Bizon Gastronomia SP Z O O</t>
+          <t>Echo Gastronomia SP Z O O</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Bizon Tekstylia Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Oaza Tekstylia Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Bizon Motoryzacja S.A.</t>
+          <t>Uran Motoryzacja S.A.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Bizon Ubezpieczenia SA</t>
+          <t>Orzeł Ubezpieczenia SA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Bizon Spawalnictwo S. A.</t>
+          <t>Narew Spawalnictwo S. A.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Bizon Ślusarstwo Spółka Akcyjna</t>
+          <t>Granit Ślusarstwo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Bizon Krawiectwo sp. z o.o.</t>
+          <t>Zorza Krawiectwo sp. z o.o.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Bizon Ochrona sp z oo</t>
+          <t>Kasprowy Ochrona sp z oo</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -9971,7 +9971,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Bizon Catering sp. z o. o.</t>
+          <t>Sudety Catering sp. z o. o.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -10048,7 +10048,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Bizon Księgowość Sp. z o.o.</t>
+          <t>Echo Księgowość Sp. z o.o.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -10125,7 +10125,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Canyon Budownictwo SP Z O O</t>
+          <t>Tytan Budownictwo SP Z O O</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -10202,7 +10202,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Canyon Transport spółka z ograniczoną odpowiedzialnością</t>
+          <t>Sokół Transport spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Canyon Spedycja Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Pilica Spedycja Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Canyon Logistyka S.A.</t>
+          <t>Topaz Logistyka S.A.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Canyon Handel SA</t>
+          <t>Olimp Handel SA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Canyon Usługi S. A.</t>
+          <t>Rysy Usługi S. A.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -10587,7 +10587,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Canyon Finanse Spółka Akcyjna</t>
+          <t>Bałtyk Finanse Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Canyon Doradztwo sp. z o.o.</t>
+          <t>Delfin Doradztwo sp. z o.o.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Canyon Szkolenia sp z oo</t>
+          <t>Ikar Szkolenia sp z oo</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Canyon Media sp. z o. o.</t>
+          <t>Neon Media sp. z o. o.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -10895,7 +10895,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PPHU Canyon Reklama</t>
+          <t>PPHU Tytan Reklama</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -10972,7 +10972,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Canyon Marketing SP Z O O</t>
+          <t>Sokół Marketing SP Z O O</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Canyon Druk spółka z ograniczoną odpowiedzialnością</t>
+          <t>Pilica Druk spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Canyon Informatyka Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Topaz Informatyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -11203,7 +11203,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Canyon Oprogramowanie S.A.</t>
+          <t>Olimp Oprogramowanie S.A.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Canyon Rolnictwo SA</t>
+          <t>Rysy Rolnictwo SA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -11357,7 +11357,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Canyon Ogrodnictwo S. A.</t>
+          <t>Bałtyk Ogrodnictwo S. A.</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Canyon Produkcja Spółka Akcyjna</t>
+          <t>Delfin Produkcja Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -11511,7 +11511,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Canyon Przemysł sp. z o.o.</t>
+          <t>Ikar Przemysł sp. z o.o.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Canyon Ekologia sp z oo</t>
+          <t>Neon Ekologia sp z oo</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Canyon Energetyka sp. z o. o.</t>
+          <t>Tytan Energetyka sp. z o. o.</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Canyon Instalacje Sp. z o.o.</t>
+          <t>Sokół Instalacje Sp. z o.o.</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Canyon Nieruchomości SP Z O O</t>
+          <t>Pilica Nieruchomości SP Z O O</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Canyon Inwestycje spółka z ograniczoną odpowiedzialnością</t>
+          <t>Topaz Inwestycje spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Canyon Medycyna Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Olimp Medycyna Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Canyon Zdrowie S.A.</t>
+          <t>Rysy Zdrowie S.A.</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Canyon Urody SA</t>
+          <t>Bałtyk Urody SA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Canyon Turystyka S. A.</t>
+          <t>Delfin Turystyka S. A.</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -12244,7 +12244,7 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Cezar</t>
+          <t>Cezary</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Canyon Rozrywka Spółka Akcyjna</t>
+          <t>Ikar Rozrywka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Canyon Gastronomia sp. z o.o.</t>
+          <t>Neon Gastronomia sp. z o.o.</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -12512,7 +12512,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Canyon Tekstylia sp. z o. o.</t>
+          <t>Sokół Tekstylia sp. z o. o.</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -12589,7 +12589,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Canyon Motoryzacja Sp. z o.o.</t>
+          <t>Pilica Motoryzacja Sp. z o.o.</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -12666,7 +12666,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Canyon Ubezpieczenia SP Z O O</t>
+          <t>Topaz Ubezpieczenia SP Z O O</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -12743,7 +12743,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Canyon Spawalnictwo spółka z ograniczoną odpowiedzialnością</t>
+          <t>Olimp Spawalnictwo spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -12820,7 +12820,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Canyon Ślusarstwo Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Rysy Ślusarstwo Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Canyon Krawiectwo S.A.</t>
+          <t>Bałtyk Krawiectwo S.A.</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Canyon Ochrona SA</t>
+          <t>Delfin Ochrona SA</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -13051,7 +13051,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Canyon Catering S. A.</t>
+          <t>Ikar Catering S. A.</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Canyon Księgowość Spółka Akcyjna</t>
+          <t>Neon Księgowość Spółka Akcyjna</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
